--- a/AAII_Financials/Quarterly/JMREY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JMREY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>JMREY</t>
   </si>
@@ -656,76 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +769,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +813,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +877,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +963,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1007,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1051,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1068,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1110,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1154,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1174,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,8 +1216,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1223,8 +1260,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,8 +1304,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,8 +1348,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1392,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,8 +1436,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1428,8 +1480,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1524,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1700,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1674,8 +1744,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +1788,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,8 +1832,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1797,54 +1876,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,377 +1963,405 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>483200</v>
+      </c>
+      <c r="E41" s="3">
         <v>478200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>479900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>413000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>230800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>316800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>371700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>438000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>489700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>406100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>445200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>542900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>567700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>203900</v>
+      </c>
+      <c r="E42" s="3">
         <v>204200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>139000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>47100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>46200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>42800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>40000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>29100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>36000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>21300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>503800</v>
+      </c>
+      <c r="E43" s="3">
         <v>483200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>484600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>462200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>427200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>447100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>330900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>344300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>344900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>369800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>330700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>366700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>367600</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>528000</v>
+      </c>
+      <c r="E44" s="3">
         <v>448600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>397000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>400400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>431800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>390500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>298400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>237800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>227500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>331300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>312100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>268600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>227900</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E45" s="3">
         <v>44200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>122300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>36500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>55100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1756900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1658300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1543700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1445000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1172300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1252300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1053800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1090200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1117000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1166800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1246100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1238800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1207600</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E47" s="3">
         <v>5800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>101700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>120400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>142200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2700</v>
       </c>
       <c r="O47" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>493800</v>
+      </c>
+      <c r="E48" s="3">
         <v>480100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>471500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>454900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>443800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>427200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>421700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>402900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>371000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>351600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>380400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>274600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>263600</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E49" s="3">
         <v>50300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>50100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>49300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>49500</v>
-      </c>
-      <c r="H49" s="3">
-        <v>45100</v>
       </c>
       <c r="I49" s="3">
         <v>45100</v>
       </c>
       <c r="J49" s="3">
+        <v>45100</v>
+      </c>
+      <c r="K49" s="3">
         <v>33200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>29900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>29900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>30300</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2445,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E52" s="3">
         <v>114300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>111700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>80100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>167500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>44900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>44100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>36000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2424600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2313800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2191300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2067600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1867700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1898400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1684800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1579500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1565000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1607100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1667800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1561900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1525600</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,213 +2615,229 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>756700</v>
+      </c>
+      <c r="E57" s="3">
         <v>607800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>511400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>432400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>472800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>538500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>419000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>337100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>356700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>379800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>410300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>380100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>316400</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>172500</v>
+      </c>
+      <c r="E58" s="3">
         <v>246000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>265800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>193500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>170800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>144300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>80100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>78500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>101000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>28200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>57600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>63200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E59" s="3">
         <v>62000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>57200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>95300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>59100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>48000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>44500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>62100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>68600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>80100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>53900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>62900</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1020300</v>
+      </c>
+      <c r="E60" s="3">
         <v>924600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>855700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>729700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>711900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>733700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>559800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>467600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>528400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>482900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>561800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>501700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>480600</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>182600</v>
+      </c>
+      <c r="E61" s="3">
         <v>192700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>185600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>260200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>90100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>118800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>107700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>106400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>67900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>100000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>78000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>69500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>69700</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2731,8 +2877,11 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1255900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1168500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1092800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1037500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>849600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>895800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>709700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>615300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>630400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>617100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>675300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>591200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>312400</v>
+      </c>
+      <c r="E72" s="3">
         <v>311900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>280200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>241600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>252200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>251900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>228200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>223900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>220300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>269000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>257900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>240900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1150400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1130300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1080900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1014600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1003200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>988200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>961200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>961000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>932700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>987800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>990200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>970000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>954800</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,54 +3511,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,8 +3604,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +3624,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>22100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-11200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10400</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>19600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-9300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>13100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-5900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E89" s="3">
         <v>51900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>78900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>49200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-48300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>130200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-85200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>98800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49900</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +3950,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-21600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-51300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14400</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4080,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-72400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-71600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-146900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-35500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-76800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17800</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4144,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E96" s="3">
         <v>2700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>36400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>21400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>19900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>43300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>700</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>26600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,127 +4318,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-131500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>178800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>15500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>42600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>30200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-30300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-50300</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-44700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>42200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>226400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-76700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-75500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-43900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>80200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-112100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-49600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15900</v>
       </c>
     </row>
